--- a/results/Int All Data 0.5/Rando_8_permute.xlsx
+++ b/results/Int All Data 0.5/Rando_8_permute.xlsx
@@ -440,247 +440,247 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8271119842829077</v>
+        <v>0.8172888015717092</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8290766208251473</v>
+        <v>0.8212180746561886</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8310412573673871</v>
+        <v>0.8192534381139489</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8290766208251473</v>
+        <v>0.8212180746561886</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8280943025540275</v>
+        <v>0.8212180746561886</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8231827111984282</v>
+        <v>0.825147347740668</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8231827111984282</v>
+        <v>0.8153241650294696</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8231827111984282</v>
+        <v>0.8153241650294696</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.825147347740668</v>
+        <v>0.8153241650294696</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.825147347740668</v>
+        <v>0.8182711198428291</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.825147347740668</v>
+        <v>0.8182711198428291</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8202357563850687</v>
+        <v>0.8133595284872299</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8222003929273085</v>
+        <v>0.8055009823182711</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8222003929273085</v>
+        <v>0.6915520628683693</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8231827111984282</v>
+        <v>0.6768172888015718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8231827111984282</v>
+        <v>0.6719056974459725</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8271119842829077</v>
+        <v>0.6709233791748527</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7927308447937131</v>
+        <v>0.6719056974459725</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7809430255402751</v>
+        <v>0.6719056974459725</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7809430255402751</v>
+        <v>0.6699410609037328</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7809430255402751</v>
+        <v>0.6709233791748527</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7838899803536346</v>
+        <v>0.6709233791748527</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7838899803536346</v>
+        <v>0.6709233791748527</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7838899803536346</v>
+        <v>0.6689587426326129</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7838899803536346</v>
+        <v>0.6689587426326129</v>
       </c>
     </row>
     <row r="27">
@@ -690,1297 +690,1297 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7858546168958742</v>
+        <v>0.6660117878192534</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7858546168958742</v>
+        <v>0.6640471512770137</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7878192534381139</v>
+        <v>0.6660117878192534</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.769155206286837</v>
+        <v>0.6650294695481336</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.769155206286837</v>
+        <v>0.6660117878192534</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7622789783889981</v>
+        <v>0.6660117878192534</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7632612966601179</v>
+        <v>0.6660117878192534</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7495088408644401</v>
+        <v>0.6650294695481336</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7554027504911591</v>
+        <v>0.6650294695481336</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7475442043222004</v>
+        <v>0.6777996070726915</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7524557956777996</v>
+        <v>0.706286836935167</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7514734774066798</v>
+        <v>0.706286836935167</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7455795677799607</v>
+        <v>0.7053045186640472</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7357563850687623</v>
+        <v>0.706286836935167</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7161100196463654</v>
+        <v>0.6866404715127701</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7151277013752456</v>
+        <v>0.693516699410609</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7324878868470426</v>
+        <v>0.6984282907662083</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7269332086747231</v>
+        <v>0.6954813359528487</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7308624817592025</v>
+        <v>0.6925343811394892</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7472226609138403</v>
+        <v>0.6843542915621703</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7524557956777996</v>
+        <v>0.6846758349705304</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7554027504911591</v>
+        <v>0.6836935166994106</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7671905697445973</v>
+        <v>0.6823896550199307</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7554027504911591</v>
+        <v>0.6823896550199307</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7603143418467584</v>
+        <v>0.6869797029671697</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7671905697445973</v>
+        <v>0.6869797029671697</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7514734774066798</v>
+        <v>0.6869797029671697</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7534381139489195</v>
+        <v>0.6876404778299294</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7465618860510805</v>
+        <v>0.6866581595588096</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7377210216110019</v>
+        <v>0.6856758412876898</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7377210216110019</v>
+        <v>0.6873012463755299</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7229862475442044</v>
+        <v>0.6666725626820131</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7229862475442044</v>
+        <v>0.6676548809531331</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7190569744597249</v>
+        <v>0.643096924175137</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7141453831041258</v>
+        <v>0.6424361493123772</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7013752455795678</v>
+        <v>0.6316306483300589</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.693516699410609</v>
+        <v>0.6316306483300589</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7020360204423275</v>
+        <v>0.6316306483300589</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7069476117979268</v>
+        <v>0.6296660117878192</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7102161100196464</v>
+        <v>0.6296660117878192</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7102161100196464</v>
+        <v>0.6110019646365422</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7220039292730844</v>
+        <v>0.6168958742632613</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7220039292730844</v>
+        <v>0.6168958742632613</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7082514734774067</v>
+        <v>0.600196463654224</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6768172888015718</v>
+        <v>0.6031434184675835</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6758349705304518</v>
+        <v>0.6139489194499017</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6846758349705304</v>
+        <v>0.6139489194499017</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6827111984282908</v>
+        <v>0.6237721021611002</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6925343811394892</v>
+        <v>0.6237721021611002</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7387033398821218</v>
+        <v>0.6313091049216988</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7445972495088409</v>
+        <v>0.6319698797844585</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7347740667976425</v>
+        <v>0.6319698797844585</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7357563850687623</v>
+        <v>0.6349522106898969</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7357563850687623</v>
+        <v>0.6385422523199767</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7180746561886051</v>
+        <v>0.6382383969576561</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.743614931237721</v>
+        <v>0.6424538373584167</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.743614931237721</v>
+        <v>0.645079248763416</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7632789847061574</v>
+        <v>0.6532770263867744</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7688513509245163</v>
+        <v>0.6542593446578943</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7659043961111567</v>
+        <v>0.6414715190872968</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7482049791849601</v>
+        <v>0.6654040770946121</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7482049791849601</v>
+        <v>0.6654040770946121</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7256116589492038</v>
+        <v>0.6654040770946121</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7157884762380053</v>
+        <v>0.656937820201012</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7629397532517578</v>
+        <v>0.6507400552119723</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7606535733011579</v>
+        <v>0.6448284575392138</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7639220715228776</v>
+        <v>0.651043910574293</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7658867080651173</v>
+        <v>0.6497577369408525</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.755081207082799</v>
+        <v>0.6497577369408525</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7285586137625633</v>
+        <v>0.60814345005338</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7118592031535259</v>
+        <v>0.6091080802784604</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7098945666112862</v>
+        <v>0.6051964952400205</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7334702051181625</v>
+        <v>0.5963733188459813</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7334702051181625</v>
+        <v>0.596677174208302</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7334702051181625</v>
+        <v>0.5796031560527861</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7344525233892824</v>
+        <v>0.5822285674577856</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7344525233892824</v>
+        <v>0.6146804464968193</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7488657540477198</v>
+        <v>0.6140373596800991</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7414702556554369</v>
+        <v>0.6228782241201776</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7414702556554369</v>
+        <v>0.6035357140601014</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7336293975325175</v>
+        <v>0.6025533957889816</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7263223393704319</v>
+        <v>0.5858186090878654</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7391101649410292</v>
+        <v>0.5861401524962255</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.7391101649410292</v>
+        <v>0.5861401524962255</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.7440217562966285</v>
+        <v>0.5913909753062243</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.7440217562966285</v>
+        <v>0.5936948433028636</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7440217562966285</v>
+        <v>0.590747888489504</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.7416439775361816</v>
+        <v>0.5923909816233837</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.684920309035433</v>
+        <v>0.570779979658747</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6227480906386016</v>
+        <v>0.5724938249767845</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6147271934756379</v>
+        <v>0.5531690029627477</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6036001490849594</v>
+        <v>0.5443812026607875</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6036001490849594</v>
+        <v>0.5401303861679481</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6009071440754521</v>
+        <v>0.5362011130834686</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5992640509415726</v>
+        <v>0.5358795696751085</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6056949191087752</v>
+        <v>0.5197878697907126</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6056949191087752</v>
+        <v>0.5252155730611059</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6017656460242958</v>
+        <v>0.5010707585013171</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5487204593838243</v>
+        <v>0.5017138453180374</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5487204593838243</v>
+        <v>0.5000884402301973</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5025161245491128</v>
+        <v>0.4987845785507173</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4969614463767933</v>
+        <v>0.4952122249666769</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5015161182319534</v>
+        <v>0.4981591797800365</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5021945811407527</v>
+        <v>0.5001238163222762</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5021945811407527</v>
+        <v>0.4981945558721155</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4910852247961137</v>
+        <v>0.5014807421398746</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4920675430672335</v>
+        <v>0.5008730314152332</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.487654375580389</v>
+        <v>0.5017669094561558</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4883859026273065</v>
+        <v>0.4987845785507173</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4890997416281846</v>
+        <v>0.4991061219590774</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4883682145812671</v>
+        <v>0.4991061219590774</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4922267354815886</v>
+        <v>0.4991061219590774</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4954775456572689</v>
+        <v>0.4981945558721155</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4984099710042388</v>
+        <v>0.4981945558721155</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4984099710042388</v>
+        <v>0.4981945558721155</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4984099710042388</v>
+        <v>0.4838666068642253</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4980884275958787</v>
+        <v>0.4816158030057044</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4980884275958787</v>
+        <v>0.4838666068642253</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4980707395498392</v>
+        <v>0.4807042369187424</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4980707395498392</v>
+        <v>0.498598222351373</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5039937081093374</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4983922829581994</v>
+        <v>0.5046898590641761</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4983922829581994</v>
+        <v>0.5415132123386756</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4983922829581994</v>
+        <v>0.5011029760137461</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4987138263665595</v>
+        <v>0.5001560338347052</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4987138263665595</v>
+        <v>0.505799152237222</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4980707395498392</v>
+        <v>0.5121207335485379</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4977491961414791</v>
+        <v>0.4949020524450565</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4977491961414791</v>
+        <v>0.4996898274783795</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4977491961414791</v>
+        <v>0.4996898274783795</v>
       </c>
     </row>
   </sheetData>
